--- a/task/MXSC/Resources/PigeonStatusInstructionsConditions.xlsx
+++ b/task/MXSC/Resources/PigeonStatusInstructionsConditions.xlsx
@@ -1,133 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ishankalburge/Documents/penn/pigeons-lohi-snr-v1/Resources/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB7DDB6-DDF6-E54C-AEED-A6AECE51C3CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="23300" windowHeight="11920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="760" windowWidth="23300" windowHeight="11920" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
-  <si>
-    <t>sic_message</t>
-  </si>
-  <si>
-    <t>sic_box_show</t>
-  </si>
-  <si>
-    <t>sic_box_x</t>
-  </si>
-  <si>
-    <t>sic_box_y</t>
-  </si>
-  <si>
-    <t>sic_box_width</t>
-  </si>
-  <si>
-    <t>sic_box_height</t>
-  </si>
-  <si>
-    <t>sic_img_file</t>
-  </si>
-  <si>
-    <t>sic_seeds_scale</t>
-  </si>
-  <si>
-    <t>You will use the left and right arrows to predict Petey's choice on each trial as you see him move.</t>
-  </si>
-  <si>
-    <t>Each trial will consist of 50 steps total. You must make your decision within this time.</t>
-  </si>
-  <si>
-    <t>Choosing slowly will tend to have high accuracy but possibly waste steps. Choosing quickly will tend to have low accuracy but use fewer steps.</t>
-  </si>
-  <si>
-    <t>We show a black line where Petey starts and a white line at Petey's midpoint so you can see exactly how far away he has moved in either direction.</t>
-  </si>
-  <si>
-    <t>This section shows the settings for the current block of trials.</t>
-  </si>
-  <si>
-    <t>You will receive coins for each correct answer and may lose coins for each incorrect answer. You will also see a target score.</t>
-  </si>
-  <si>
-    <t>sun.png</t>
-  </si>
-  <si>
-    <t>In general, your performance will depend on both guessing correctly and not wasting too many steps.
-Let's get started!
-Each block will begin with a description of the conditions.</t>
-  </si>
-  <si>
-    <t>This bar will show how many steps you have used so far. Once you have used up all your steps, the block will end.</t>
-  </si>
-  <si>
-    <t>This bar tells you how many coins you have earned so far.</t>
-  </si>
-  <si>
-    <t>The experiment will consist of 5 blocks total.</t>
-  </si>
-  <si>
-    <t>You will receive a cash bonus at the end of the experiment based on your performance in each block. Earning the most number of coins in each block will maximize your cash bonus.</t>
-  </si>
-  <si>
-    <t>steps</t>
-  </si>
-  <si>
-    <t>sic_objective</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Trebuchet MS"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -191,30 +97,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -514,359 +479,449 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="186.33203125" bestFit="1" customWidth="1"/>
+    <col width="186.33203125" bestFit="1" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sic_message</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>sic_box_show</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sic_box_x</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sic_box_y</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sic_box_width</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>sic_box_height</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>sic_img_file</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>sic_seeds_scale</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>sic_objective</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>You will use the left and right arrows to predict Petey's choice on each trial as you see him move.</t>
+        </is>
       </c>
       <c r="B2" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="C2" s="1">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
+      <c r="C2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Each trial will consist of 50 steps total. You must make your decision within this time.</t>
+        </is>
       </c>
       <c r="B3" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="6">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>10</v>
+      <c r="C3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Choosing slowly will tend to have high accuracy but possibly waste steps. Choosing quickly will tend to have low accuracy but use fewer steps.</t>
+        </is>
       </c>
       <c r="B4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="6">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
+      <c r="C4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>We show a black line where Petey starts and a white line at Petey's midpoint so you can see exactly how far away he has moved in either direction.</t>
+        </is>
       </c>
       <c r="B5" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="6">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>This section shows the settings for the current block of trials.</t>
+        </is>
       </c>
       <c r="B6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C6" s="1">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6" s="1" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>You will receive coins for each correct answer and may lose coins for each incorrect answer. You will also see a target score.</t>
+        </is>
       </c>
       <c r="B7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="C7" s="1">
-        <v>-0.55000000000000004</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="C7" s="1" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="6">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>This bar tells you how many coins you have earned so far.</t>
+        </is>
       </c>
       <c r="B8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="1" t="n">
         <v>-0.15</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="1" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>This bar will show how many steps you have used so far. Once you have used up all your steps, the block will end.</t>
+        </is>
       </c>
       <c r="B9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="1" t="n">
         <v>-0.3</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>19</v>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>You will receive a cash bonus at the end of the experiment based on your performance in each block. Earning the most number of coins in each block will maximize your cash bonus.</t>
+        </is>
       </c>
       <c r="B10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="6">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
+      <c r="C10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>The experiment will consist of 4 blocks total.</t>
+        </is>
       </c>
       <c r="B11" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="40" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>15</v>
+      <c r="C11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>In general, your performance will depend on both guessing correctly and not wasting too many steps.
+Let's get started!
+Each block will begin with a description of the conditions.</t>
+        </is>
       </c>
       <c r="B12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>sun.png</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>steps</t>
+        </is>
       </c>
     </row>
   </sheetData>
